--- a/evaluation_forms/017_program_evaluation_checklist--evaluation_forms.xlsx
+++ b/evaluation_forms/017_program_evaluation_checklist--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Program Evaluation Checklist</t>
+          <t>Program Evaluation Checklist Overview</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_2</t>
+          <t>evaluation_criteria</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_3</t>
+          <t>evaluation_methods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_4</t>
+          <t>stakeholders_involved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_5</t>
+          <t>evaluation_schedule</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_6</t>
+          <t>evaluation_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_7</t>
+          <t>evaluation_tools</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -676,12 +676,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_8</t>
+          <t>evaluation_process</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_9</t>
+          <t>evaluation_outcomes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_10</t>
+          <t>review_revision</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -745,12 +745,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_11</t>
+          <t>evaluation_report</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_12</t>
+          <t>evaluation_timeline</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -783,305 +783,6 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Program Evaluation Checklist</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Evaluation Criteria</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Evaluation Methods</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Stakeholders Involved</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Evaluation Frequency</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Evaluation Tools</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Evaluation Process</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Evaluation Outcomes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Review and Revision</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Evaluation Report</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Evaluation Timeline</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Recommendations</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,58 +827,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_2_choices</t>
+          <t>evaluation_criteria_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>evaluation_of_program_outcomes</t>
+          <t>program_goals</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Evaluation of program outcomes</t>
+          <t>Program goals</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_2_choices</t>
+          <t>evaluation_criteria_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>evaluation_of_program_process</t>
+          <t>program_objectives</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Evaluation of program process</t>
+          <t>Program objectives</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_2_choices</t>
+          <t>evaluation_criteria_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>evaluation_of_program_management</t>
+          <t>outcome_metrics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Evaluation of program management</t>
+          <t>Outcome metrics</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_3_choices</t>
+          <t>evaluation_methods_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_3_choices</t>
+          <t>evaluation_methods_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_3_choices</t>
+          <t>evaluation_methods_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_4_choices</t>
+          <t>stakeholders_involved_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_4_choices</t>
+          <t>stakeholders_involved_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_4_choices</t>
+          <t>stakeholders_involved_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_6_choices</t>
+          <t>evaluation_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_6_choices</t>
+          <t>evaluation_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_6_choices</t>
+          <t>evaluation_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_7_choices</t>
+          <t>evaluation_tools_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_7_choices</t>
+          <t>evaluation_tools_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_7_choices</t>
+          <t>evaluation_tools_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,204 +1082,102 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_8_choices</t>
+          <t>evaluation_outcomes_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>systematic</t>
+          <t>increased_knowledge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Systematic</t>
+          <t>Increased knowledge</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_8_choices</t>
+          <t>evaluation_outcomes_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>iterative</t>
+          <t>improved_behavior</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iterative</t>
+          <t>Improved behavior</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_8_choices</t>
+          <t>evaluation_outcomes_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>continuous</t>
+          <t>enhanced_skills</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Continuous</t>
+          <t>Enhanced skills</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_9_choices</t>
+          <t>review_revision_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>increased_knowledge</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Increased knowledge</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_9_choices</t>
+          <t>review_revision_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>improved_behavior</t>
+          <t>periodically</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Improved behavior</t>
+          <t>Periodically</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>program_evaluation_checklist_page_9_choices</t>
+          <t>review_revision_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>enhanced_skills</t>
+          <t>as_needed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Enhanced skills</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>regularly</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Regularly</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>periodically</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Periodically</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_10_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>as_needed</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
           <t>As needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>semiannually</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Semiannually</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>program_evaluation_checklist_page_11_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>annually</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annually</t>
         </is>
       </c>
     </row>
